--- a/src/test/resources/testData/organisation/stf/stf_organisation_many_errors.xlsx
+++ b/src/test/resources/testData/organisation/stf/stf_organisation_many_errors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karthik.jaladurgam/Desktop/STOS/Test data/Business/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karthik.jaladurgam/workspace/securities-transfer-charge-submissions-ui-tests/src/test/resources/testData/organisation/stf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F9F772-D5FB-2B4D-BB40-2DEC35F0BC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA5C9CC-BAB4-A345-818D-0884383746E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,9 +64,6 @@
     <t>Seller's address - country</t>
   </si>
   <si>
-    <t>Is the business and the seller connected persons?</t>
-  </si>
-  <si>
     <t>Is the business applying for a relief?</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
   <si>
     <t xml:space="preserve">What is the tax rate for this transaction?
 </t>
-  </si>
-  <si>
-    <t>What type of securities are you buying?</t>
   </si>
   <si>
     <t>How many securities are you buying?</t>
@@ -198,9 +192,6 @@
 (Mandatory if shares are the type of security being transfered)</t>
   </si>
   <si>
-    <t>For example; shares (include the share type), interests in underlying securities, loan notes or other debt securities, or other type of securities.</t>
-  </si>
-  <si>
     <t>Enter an amount in GBP. For example, £600.00 or £193.54.
 Enter the amount of consideration given in exchange for these securities as a cash amount.
 You do not need to provide details about conversion or exchange rates, or how valuations of non-monetary items were made.</t>
@@ -319,6 +310,16 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>Are the business and the seller connected persons?</t>
+  </si>
+  <si>
+    <t>What class or type of shares are being transfered?</t>
+  </si>
+  <si>
+    <t>For example ordinary, preference or any other share class or type. 
+(Mandatory if shares are the type of security being bought)</t>
   </si>
 </sst>
 </file>
@@ -360,13 +361,6 @@
     <font>
       <u/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -377,6 +371,12 @@
       <color theme="10"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -399,18 +399,9 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -419,7 +410,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -439,14 +430,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -676,68 +669,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="I1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="N1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="P1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="P1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="S1" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U1" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="R1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S1" t="s">
-        <v>51</v>
-      </c>
-      <c r="T1" t="s">
-        <v>64</v>
-      </c>
-      <c r="U1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:42" ht="153" x14ac:dyDescent="0.2">
@@ -745,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -769,40 +762,40 @@
         <v>7</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
@@ -828,63 +821,63 @@
     </row>
     <row r="3" spans="1:42" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="R3" s="5" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="S3" s="5"/>
       <c r="T3" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
@@ -912,46 +905,46 @@
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
         <v>123456789</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="7">
         <v>46753</v>
       </c>
-      <c r="P4" s="10" t="s">
-        <v>69</v>
+      <c r="P4" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="Q4" s="5">
         <v>9.5</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="U4" s="5">
         <v>-200</v>
@@ -980,51 +973,51 @@
     <row r="5" spans="1:42" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N5" s="5">
         <v>12345678</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="7">
         <v>46023</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="5">
         <v>0.5</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="S5" s="5">
         <v>15000</v>
@@ -1059,51 +1052,51 @@
     <row r="6" spans="1:42" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N6" s="5">
         <v>12345678</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <v>46023</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q6" s="5">
         <v>0.5</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="S6" s="5">
         <v>15000</v>
@@ -1138,51 +1131,51 @@
     <row r="7" spans="1:42" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N7" s="5">
         <v>12345678</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="7">
         <v>46023</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q7" s="5">
         <v>0.5</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="S7" s="5">
         <v>15000</v>
@@ -1217,51 +1210,51 @@
     <row r="8" spans="1:42" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N8" s="5">
         <v>12345678</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="7">
         <v>46023</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q8" s="5">
         <v>0.5</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="S8" s="5">
         <v>15000</v>
@@ -1295,9 +1288,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="T4" r:id="rId2" xr:uid="{66919BAE-54CA-0F4B-9360-CE1BAE641159}"/>
-    <hyperlink ref="P4" r:id="rId3" xr:uid="{DFFBC104-475A-2247-A3F6-3923931EFFDE}"/>
+    <hyperlink ref="T4" r:id="rId1" xr:uid="{66919BAE-54CA-0F4B-9360-CE1BAE641159}"/>
+    <hyperlink ref="P4" r:id="rId2" xr:uid="{DFFBC104-475A-2247-A3F6-3923931EFFDE}"/>
+    <hyperlink ref="L3" r:id="rId3" xr:uid="{6F10CBA3-54C2-3543-AEB4-F502F0673A7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
